--- a/media/Levels/kakeraMapLevel4.xlsx
+++ b/media/Levels/kakeraMapLevel4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCC8D03-57F0-42E1-BA15-56D994125DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4C732F-1F35-431C-A75A-E39B38F49D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2593B2BE-8BB6-4BBC-9A1E-BE5DFE42D0E8}"/>
+    <workbookView xWindow="2508" yWindow="0" windowWidth="15660" windowHeight="12168" xr2:uid="{2593B2BE-8BB6-4BBC-9A1E-BE5DFE42D0E8}"/>
   </bookViews>
   <sheets>
     <sheet name="MapDateLevels" sheetId="1" r:id="rId1"/>
@@ -39687,13 +39687,13 @@
         <v>1</v>
       </c>
       <c r="BW86" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BX86" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BY86" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BZ86" s="6">
         <v>1</v>
@@ -40130,10 +40130,10 @@
         <v>0</v>
       </c>
       <c r="BT87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV87" s="6">
         <v>1</v>
@@ -40142,7 +40142,7 @@
         <v>1</v>
       </c>
       <c r="BX87" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BY87" s="6">
         <v>1</v>
@@ -40151,7 +40151,7 @@
         <v>1</v>
       </c>
       <c r="CA87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB87">
         <v>0</v>
@@ -40582,28 +40582,28 @@
         <v>0</v>
       </c>
       <c r="BT88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW88" s="6">
         <v>1</v>
       </c>
       <c r="BX88" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BY88" s="6">
         <v>1</v>
       </c>
       <c r="BZ88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB88">
         <v>0</v>
@@ -41034,13 +41034,13 @@
         <v>0</v>
       </c>
       <c r="BT89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW89" s="6">
         <v>1</v>
@@ -41052,10 +41052,10 @@
         <v>1</v>
       </c>
       <c r="BZ89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB89">
         <v>0</v>
@@ -41486,13 +41486,13 @@
         <v>0</v>
       </c>
       <c r="BT90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW90" s="6">
         <v>1</v>
@@ -41504,10 +41504,10 @@
         <v>1</v>
       </c>
       <c r="BZ90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB90">
         <v>0</v>
@@ -41938,13 +41938,13 @@
         <v>0</v>
       </c>
       <c r="BT91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW91" s="6">
         <v>1</v>
@@ -41956,10 +41956,10 @@
         <v>1</v>
       </c>
       <c r="BZ91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB91">
         <v>0</v>
@@ -42390,13 +42390,13 @@
         <v>0</v>
       </c>
       <c r="BT92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW92" s="6">
         <v>1</v>
@@ -42408,10 +42408,10 @@
         <v>1</v>
       </c>
       <c r="BZ92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB92">
         <v>0</v>
@@ -42842,13 +42842,13 @@
         <v>0</v>
       </c>
       <c r="BT93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW93" s="6">
         <v>1</v>
@@ -42860,10 +42860,10 @@
         <v>1</v>
       </c>
       <c r="BZ93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB93">
         <v>0</v>
@@ -43294,13 +43294,13 @@
         <v>0</v>
       </c>
       <c r="BT94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW94" s="6">
         <v>1</v>
@@ -43312,10 +43312,10 @@
         <v>1</v>
       </c>
       <c r="BZ94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB94">
         <v>0</v>
@@ -43746,13 +43746,13 @@
         <v>0</v>
       </c>
       <c r="BT95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW95" s="6">
         <v>1</v>
@@ -43764,10 +43764,10 @@
         <v>1</v>
       </c>
       <c r="BZ95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB95">
         <v>0</v>

--- a/media/Levels/kakeraMapLevel4.xlsx
+++ b/media/Levels/kakeraMapLevel4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\2024年３月特別授業\BaseCross64\DoctorRemote\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6CF8C61-5DB0-4461-B46A-236A6E8A4A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE9A6EE-4DCD-4575-BA86-EB7A88CAC8D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="576" yWindow="72" windowWidth="15660" windowHeight="12168" xr2:uid="{2739887D-75BF-488C-B937-CF17A666C93E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2739887D-75BF-488C-B937-CF17A666C93E}"/>
   </bookViews>
   <sheets>
     <sheet name="Level_4" sheetId="1" r:id="rId1"/>
@@ -40401,31 +40401,31 @@
         <v>0</v>
       </c>
       <c r="BT87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC87">
         <v>0</v>
@@ -40856,31 +40856,31 @@
         <v>0</v>
       </c>
       <c r="BT88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC88">
         <v>0</v>
@@ -41311,31 +41311,31 @@
         <v>0</v>
       </c>
       <c r="BT89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC89">
         <v>0</v>
@@ -41766,31 +41766,31 @@
         <v>0</v>
       </c>
       <c r="BT90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC90">
         <v>0</v>
@@ -42221,31 +42221,31 @@
         <v>0</v>
       </c>
       <c r="BT91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC91">
         <v>0</v>
@@ -42676,31 +42676,31 @@
         <v>0</v>
       </c>
       <c r="BT92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC92">
         <v>0</v>
@@ -43131,31 +43131,31 @@
         <v>0</v>
       </c>
       <c r="BT93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC93">
         <v>0</v>
@@ -43586,31 +43586,31 @@
         <v>0</v>
       </c>
       <c r="BT94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC94">
         <v>0</v>
@@ -44041,31 +44041,31 @@
         <v>0</v>
       </c>
       <c r="BT95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC95">
         <v>0</v>
